--- a/3_xgboost/2_datos/1_raw/2_90_10/resultados_hiperparametros_optimizados.xlsx
+++ b/3_xgboost/2_datos/1_raw/2_90_10/resultados_hiperparametros_optimizados.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Características_Seleccionadas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Mejor_Modelo_Métricas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Mejores_Hiperparámetros" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tuning_Resultados" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Búsqueda_Features" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Validación_Hiperparámetros" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Todos_Resultados_Tuning" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Búsqueda_Features" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005954985972493887</v>
+        <v>1.562986016273499</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.969550609588623</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007946372424707245</v>
+        <v>3.909759165964042</v>
       </c>
     </row>
     <row r="3">
@@ -467,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.169021129608154</v>
+        <v>6.435879230499268</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8418582677841187</v>
+        <v>0.8241419792175293</v>
       </c>
       <c r="D3" t="n">
-        <v>8.599748882796984</v>
+        <v>9.068670027187654</v>
       </c>
     </row>
   </sheetData>
@@ -532,16 +533,16 @@
         <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005668258760124445</v>
+        <v>1.167969703674316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999996423721313</v>
+        <v>0.9717234373092651</v>
       </c>
       <c r="E2" t="n">
-        <v>59.70000000000002</v>
+        <v>56.60000000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -554,16 +555,16 @@
         <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005550384521484375</v>
+        <v>1.167826294898987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999994039535522</v>
+        <v>0.9690614938735962</v>
       </c>
       <c r="E3" t="n">
-        <v>73.69999999999999</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -576,16 +577,16 @@
         <v>97.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007049560546875</v>
+        <v>1.438809037208557</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999970197677612</v>
+        <v>0.919955313205719</v>
       </c>
       <c r="E4" t="n">
-        <v>84.22499999999988</v>
+        <v>82.94999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -598,10 +599,10 @@
         <v>90</v>
       </c>
       <c r="C5" t="n">
-        <v>7.266315460205078</v>
+        <v>10.58853149414062</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6646013855934143</v>
+        <v>0.4491310119628906</v>
       </c>
       <c r="E5" t="n">
         <v>45.60000000000001</v>
@@ -620,10 +621,10 @@
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>10.49519729614258</v>
+        <v>15.53335189819336</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.022158622741699</v>
+        <v>-2.324868202209473</v>
       </c>
       <c r="E6" t="n">
         <v>66.19999999999999</v>
@@ -642,7 +643,7 @@
         <v>97.5</v>
       </c>
       <c r="C7" t="n">
-        <v>17.81951904296875</v>
+        <v>20.82762145996094</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -681,31 +682,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_1</t>
+          <t>casos_dengue_lag_2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3635270595550537</v>
+        <v>0.2882884740829468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dengue_lag_mean</t>
+          <t>casos_dengue_lag_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2671331465244293</v>
+        <v>0.2675212025642395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_2</t>
+          <t>dengue_lag_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.185424879193306</v>
+        <v>0.1389680057764053</v>
       </c>
     </row>
     <row r="5">
@@ -715,7 +716,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04084388911724091</v>
+        <v>0.08375456929206848</v>
       </c>
     </row>
     <row r="6">
@@ -725,177 +726,177 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01664832234382629</v>
+        <v>0.02611661516129971</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>temp_lag_mean</t>
+          <t>temp_lag_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01407225430011749</v>
+        <v>0.02382418140769005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>temp_lag_std</t>
+          <t>casos_dengue_lag_4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0127475755289197</v>
+        <v>0.01524694077670574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_4</t>
+          <t>sst_lag_11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01117069460451603</v>
+        <v>0.014657037332654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dengue_trend_8weeks</t>
+          <t>temp_min_lag_1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009946688078343868</v>
+        <v>0.01190257165580988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>casos_dengue_lag_10</t>
+          <t>dengue_trend_8weeks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009693490341305733</v>
+        <v>0.01039256155490875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sst_lag_11</t>
+          <t>dengue_lag_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00865728035569191</v>
+        <v>0.01012969948351383</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>temp_min_lag_1</t>
+          <t>casos_dengue_lag_10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008425947278738022</v>
+        <v>0.00994760449975729</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>soi_sst</t>
+          <t>sst_lag_3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.006415320560336113</v>
+        <v>0.009888524189591408</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>temp_min_lag_2</t>
+          <t>sst</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.005631047766655684</v>
+        <v>0.009813904762268066</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_1</t>
+          <t>año</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.005625379737466574</v>
+        <v>0.009618428535759449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vel_vi_max_lag_4</t>
+          <t>temp_min_lag_2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.004939480684697628</v>
+        <v>0.009499203413724899</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>soi_lag_6</t>
+          <t>temp_lag_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.004088175017386675</v>
+        <v>0.009090728126466274</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vel_vi_min_lag_7</t>
+          <t>soi_lag_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.004055677447468042</v>
+        <v>0.008888363838195801</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>temp_lag_1</t>
+          <t>vel_vi_max_lag_1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.003744368208572268</v>
+        <v>0.008429486304521561</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sst_lag_3</t>
+          <t>temp_lag_1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003510186914354563</v>
+        <v>0.007020444609224796</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>año</t>
+          <t>soi_sst</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.003365700365975499</v>
+        <v>0.006662692874670029</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prec_temp</t>
+          <t>vel_vi_max_lag_4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003324417164549232</v>
+        <v>0.006571954116225243</v>
       </c>
     </row>
     <row r="24">
@@ -905,27 +906,27 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.002594795310869813</v>
+        <v>0.005561557598412037</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sst</t>
+          <t>prec_temp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.002541946480050683</v>
+        <v>0.00513383885845542</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dengue_lag_sum</t>
+          <t>vel_vi_min_lag_7</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001872337772510946</v>
+        <v>0.003071341896429658</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,21 +1024,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>colsample_bytree</t>
+          <t>n_estimators</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>max_depth</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1047,67 +1048,77 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>max_depth</t>
+          <t>subsample</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>min_child_weight</t>
+          <t>colsample_bytree</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>n_estimators</t>
+          <t>min_child_weight</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reg_alpha</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reg_lambda</t>
+          <t>reg_alpha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>subsample</t>
+          <t>reg_lambda</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>random_state</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1121,699 +1132,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>colsample_bytree</t>
+          <t>Métrica</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>gamma</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>learning_rate</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>max_depth</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>min_child_weight</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_estimators</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>reg_alpha</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>reg_lambda</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subsample</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mae</t>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAE Train</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5.703387260437012</v>
+        <v>4.784356594085693</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>0.6</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAE Test</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>200</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.776851654052734</v>
+        <v>6.191939353942871</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>0.8</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R² Train</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.794191837310791</v>
+        <v>0.9226052165031433</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>0.7</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R² Test</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>400</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.795863628387451</v>
+        <v>0.8147549629211426</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>0.6</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brecha Sobreajuste</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.805860042572021</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.811815738677979</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.82814884185791</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.871988296508789</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>200</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.884096622467041</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>200</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.930066108703613</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.936367511749268</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.95102071762085</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>100</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.957199573516846</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>200</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.970733642578125</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>400</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6.038642883300781</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>200</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.03927755355835</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>100</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6.081462860107422</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>200</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6.126721382141113</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6.12750244140625</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>400</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6.128777503967285</v>
+        <v>1.407582759857178</v>
       </c>
     </row>
   </sheetData>
@@ -1827,6 +1208,1307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mae_train</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>r2_train</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mae_test</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>r2_test</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>overfit_gap</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.05, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5180556178092957</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9992058277130127</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.700057029724121</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8159825801849365</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.182001411914825</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.492834782600402</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 4, 'learning_rate': 0.03, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.179419994354248</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9650817513465881</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.755269050598145</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8286303281784058</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.575849056243896</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.483501052856445</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.747635364532471</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9754372239112854</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.777183532714844</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8214240670204163</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.029548168182373</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.678129386901856</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.970328330993652</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9716170430183411</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.798166275024414</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8173317909240723</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.827837944030762</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.610034942626953</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 4, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.98160457611084</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9681081771850586</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.802689552307129</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8214037418365479</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.821084976196289</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.610047721862793</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.156505823135376</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9644601941108704</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.834011077880859</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8174632787704468</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.677505254745483</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.571408748626709</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.867843866348267</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9686967730522156</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.837284088134766</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8211528062820435</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.969440221786499</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.690146541595459</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.126838684082031</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9635329842567444</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.837428569793701</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8182874917984009</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.71058988571167</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.586693096160888</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.3, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.130174398422241</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9635160565376282</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.843283653259277</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8185588121414185</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.713109254837036</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.59121389389038</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.05, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7002371549606323</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9982398152351379</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.845560550689697</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.811463475227356</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.145323395729065</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.565465688705444</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.03, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.007250547409058</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9873300194740295</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.854483604431152</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8121082186698914</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.847233057022095</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.051583385467529</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.06458854675293</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9960143566131592</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.907419681549072</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8045922517776489</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.842831134796143</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.481584262847901</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.939047336578369</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9456068873405457</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.914393901824951</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8260047435760498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.975346565246582</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.338774967193603</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.930647611618042</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9724171161651611</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.925506591796875</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8056792020797729</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.994858980178833</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.753247547149658</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.573378324508667</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.97635817527771</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.934697151184082</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8136757016181946</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.361318826675415</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.905345821380616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.3, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.283599138259888</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9811212420463562</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.960573196411133</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8164849877357483</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.676974058151245</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.047133541107177</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.901292085647583</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9459456205368042</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.971059799194336</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8259782791137695</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.069767713546753</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.410542964935303</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.942359447479248</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9717534184455872</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.977897167205811</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8134098052978516</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.035537719726562</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.800953388214111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.563302040100098</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9759153127670288</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.0102219581604</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8181459903717041</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.446919918060303</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.984901142120361</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.709959268569946</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9475094676017761</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.07759428024292</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8127627372741699</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.367635011672974</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.593610572814941</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.218968868255615</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9351202249526978</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.0895676612854</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8162822127342224</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.870598793029785</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.401980113983154</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 4, 'learning_rate': 0.05, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.969633936882019</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9970700740814209</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.09932804107666</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7968238592147827</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.129694104194641</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.711474466323852</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9638150334358215</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9973147511482239</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.124314785003662</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8031708002090454</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.160499751567841</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.738788771629333</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 4, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.018834352493286</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9865542054176331</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6.170440673828125</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7905356287956238</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.151606321334839</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.362906932830811</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.3, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.784356594085693</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9226052165031433</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6.191939353942871</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8147549629211426</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.407582759857178</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.278196716308594</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.3, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.9315687417984009</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9972307682037354</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.212135791778564</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8029143810272217</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.280567049980164</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.839508295059204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 4, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.056235432624817</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9966257810592651</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.252490997314453</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.79442298412323</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.196255564689636</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.829996824264526</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.709128737449646</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9908968210220337</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.265503406524658</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7967897057533264</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.556374669075012</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.5818519115448</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.03, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.775590062141418</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9903522133827209</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.274357318878174</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7952649593353271</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.498767256736755</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.564121294021606</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.566880345344543</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9924831390380859</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6.281027793884277</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7957417964935303</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.714147448539734</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.65427565574646</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.03, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.8882818222045898</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9973740577697754</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6.315486907958984</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7970296740531921</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.427205085754395</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.960174179077148</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3.985287427902222</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.9415509104728699</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6.357019424438477</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8079191446304321</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.371731996536255</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.762904453277588</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.00875997543335</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.9340552091598511</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6.357953548431396</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8070343732833862</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.349193572998047</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.754449558258057</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.9933062791824341</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9970471262931824</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6.359469890594482</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7913501858711243</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.366163611412048</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.962147378921509</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4.305123329162598</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9297301769256592</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6.383328914642334</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8058573603630066</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.078205585479736</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.661279582977295</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.3, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.49884557723999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.920864999294281</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.462102890014648</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.804286003112793</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.963257312774658</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.662564659118652</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5.012535572052002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9100118279457092</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6.465143203735352</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8074718713760376</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.45260763168335</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.460128974914551</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7.914801120758057</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7741062641143799</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8.323880195617676</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7173696160316467</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.4090790748596191</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.157959747314453</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7.645612239837646</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7858494520187378</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8.335330009460449</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7175655364990234</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6897177696228027</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5.27708511352539</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7.64894962310791</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7857779264450073</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.34797477722168</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7172818183898926</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6990251541137695</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.288394927978516</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7.579153060913086</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7937147617340088</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8.404927253723145</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7100127935409546</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8257741928100586</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.37326602935791</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.1, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>8.053467750549316</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7739365100860596</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8.408405303955078</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7142393589019775</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.3549375534057617</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.187018203735351</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.1, 'reg_alpha': 0.5, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8.096525192260742</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.7711905241012573</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8.417233467102051</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7100237607955933</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3207082748413086</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.178623390197753</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8.052731513977051</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.7738012671470642</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.418901443481445</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7142959833145142</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.3661699295043945</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.197808837890625</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.3, 'reg_alpha': 0.3, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>8.150474548339844</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.7635706663131714</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8.484677314758301</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7110446691513062</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.334202766418457</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.224487495422363</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7.962116241455078</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7652173042297363</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8.524662017822266</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7021212577819824</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5625457763671875</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.339815521240234</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 1.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>8.095793724060059</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7704086303710938</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.540868759155273</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7039842009544373</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4450750350952148</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5.30255126953125</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 4, 'learning_rate': 0.01, 'subsample': 0.8, 'colsample_bytree': 0.8, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8.038010597229004</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7626723647117615</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8.578437805175781</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6993975043296814</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5404272079467773</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.363233566284179</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 5, 'gamma': 0.5, 'reg_alpha': 0.1, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8.104077339172363</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7525701522827148</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8.668642997741699</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6891162991523743</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5645656585693359</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.427012062072754</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'subsample': 0.7, 'colsample_bytree': 0.7, 'min_child_weight': 3, 'gamma': 0.5, 'reg_alpha': 0.5, 'reg_lambda': 2.0, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7.967806339263916</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7591458559036255</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8.883061408996582</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6798709630966187</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.915255069732666</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.695938873291015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
